--- a/Data/KeywordMapping.xlsx
+++ b/Data/KeywordMapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Chimbu/Desktop/Work/Personal/DataAnalytics/CBAnalytics/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54EB068-D5DC-7049-95B7-3AFD3C16958F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3227A461-B2D3-FB4A-B722-EEEB2EF9F853}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="262">
   <si>
     <t>Commerz Bank</t>
   </si>
@@ -360,9 +360,6 @@
     <t>DM FIL</t>
   </si>
   <si>
-    <t>T.S.</t>
-  </si>
-  <si>
     <t>Infoscore Forderungsmana</t>
   </si>
   <si>
@@ -799,6 +796,24 @@
   </si>
   <si>
     <t>Rundfunk</t>
+  </si>
+  <si>
+    <t>Smyths</t>
+  </si>
+  <si>
+    <t>SUPERMARKT</t>
+  </si>
+  <si>
+    <t>TASCHEN</t>
+  </si>
+  <si>
+    <t>TASCHEN PARADIES</t>
+  </si>
+  <si>
+    <t>LOTUS</t>
+  </si>
+  <si>
+    <t>Vivantes</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.5" style="2" customWidth="1"/>
@@ -1201,8 +1216,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>110</v>
+      <c r="A6" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1235,7 +1250,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -1246,7 +1261,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1257,7 +1272,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -1268,7 +1283,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -1312,7 +1327,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>11</v>
@@ -1323,7 +1338,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1334,7 +1349,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>13</v>
@@ -1345,7 +1360,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
@@ -1378,7 +1393,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>17</v>
@@ -1400,7 +1415,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>19</v>
@@ -1477,7 +1492,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>26</v>
@@ -1499,7 +1514,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>28</v>
@@ -1521,10 +1536,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>89</v>
@@ -1532,7 +1547,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>30</v>
@@ -1543,7 +1558,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>31</v>
@@ -1565,7 +1580,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>0</v>
@@ -1587,7 +1602,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>34</v>
@@ -1598,7 +1613,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>35</v>
@@ -1609,7 +1624,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>36</v>
@@ -1620,7 +1635,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>36</v>
@@ -1631,7 +1646,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>36</v>
@@ -1642,7 +1657,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>36</v>
@@ -1653,7 +1668,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>36</v>
@@ -1664,7 +1679,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>36</v>
@@ -1675,7 +1690,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>36</v>
@@ -1708,7 +1723,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>39</v>
@@ -1719,7 +1734,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>40</v>
@@ -1730,7 +1745,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>41</v>
@@ -1763,12 +1778,12 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>44</v>
@@ -1790,7 +1805,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>46</v>
@@ -1801,7 +1816,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>47</v>
@@ -1856,7 +1871,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>52</v>
@@ -1867,7 +1882,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>53</v>
@@ -1878,7 +1893,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>54</v>
@@ -1922,7 +1937,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>58</v>
@@ -1933,7 +1948,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>59</v>
@@ -1955,7 +1970,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>26</v>
@@ -1966,7 +1981,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>61</v>
@@ -1977,7 +1992,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>62</v>
@@ -1988,7 +2003,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>63</v>
@@ -1999,7 +2014,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>26</v>
@@ -2010,7 +2025,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>64</v>
@@ -2021,7 +2036,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>64</v>
@@ -2032,7 +2047,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>0</v>
@@ -2065,7 +2080,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>67</v>
@@ -2109,7 +2124,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>71</v>
@@ -2120,7 +2135,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>72</v>
@@ -2131,7 +2146,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>73</v>
@@ -2142,7 +2157,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>74</v>
@@ -2153,7 +2168,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>75</v>
@@ -2164,7 +2179,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>75</v>
@@ -2208,7 +2223,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>75</v>
@@ -2219,7 +2234,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>79</v>
@@ -2230,7 +2245,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>14</v>
@@ -2252,7 +2267,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>81</v>
@@ -2263,7 +2278,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>82</v>
@@ -2329,7 +2344,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>30</v>
@@ -2340,10 +2355,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>105</v>
@@ -2351,10 +2366,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>64</v>
@@ -2362,7 +2377,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>0</v>
@@ -2373,10 +2388,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>99</v>
@@ -2384,10 +2399,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>106</v>
@@ -2395,10 +2410,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>99</v>
@@ -2406,10 +2421,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>89</v>
@@ -2417,10 +2432,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>99</v>
@@ -2428,10 +2443,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>95</v>
@@ -2439,10 +2454,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>103</v>
@@ -2450,10 +2465,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>89</v>
@@ -2461,21 +2476,21 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>92</v>
@@ -2483,10 +2498,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>103</v>
@@ -2494,10 +2509,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>99</v>
@@ -2505,7 +2520,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>0</v>
@@ -2516,10 +2531,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>106</v>
@@ -2527,10 +2542,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>105</v>
@@ -2538,21 +2553,21 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>94</v>
@@ -2560,10 +2575,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>95</v>
@@ -2571,10 +2586,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -2582,10 +2597,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>92</v>
@@ -2593,10 +2608,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>101</v>
@@ -2604,7 +2619,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>19</v>
@@ -2615,10 +2630,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>95</v>
@@ -2626,10 +2641,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>105</v>
@@ -2637,21 +2652,21 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>103</v>
@@ -2659,10 +2674,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>95</v>
@@ -2670,18 +2685,18 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>19</v>
@@ -2692,10 +2707,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>95</v>
@@ -2703,7 +2718,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>17</v>
@@ -2714,10 +2729,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>94</v>
@@ -2725,10 +2740,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>105</v>
@@ -2736,10 +2751,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>106</v>
@@ -2747,43 +2762,43 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>95</v>
@@ -2791,10 +2806,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>97</v>
@@ -2802,10 +2817,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>94</v>
@@ -2813,10 +2828,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>92</v>
@@ -2824,10 +2839,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>99</v>
@@ -2835,18 +2850,18 @@
     </row>
     <row r="155" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>44</v>
@@ -2857,21 +2872,21 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>103</v>
@@ -2879,10 +2894,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>104</v>
@@ -2890,10 +2905,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>95</v>
@@ -2901,7 +2916,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>0</v>
@@ -2912,10 +2927,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>101</v>
@@ -2923,7 +2938,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>38</v>
@@ -2934,10 +2949,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>95</v>
@@ -2945,10 +2960,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>97</v>
@@ -2956,32 +2971,32 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>103</v>
@@ -2989,10 +3004,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>95</v>
@@ -3000,10 +3015,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>101</v>
@@ -3011,10 +3026,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>89</v>
@@ -3022,10 +3037,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>64</v>
@@ -3033,10 +3048,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>103</v>
@@ -3044,10 +3059,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>103</v>
@@ -3055,13 +3070,57 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179" s="2">
+        <v>511678154</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
